--- a/outputs_xlsx_solution/test_new4.4-wide-NF-1.xlsx
+++ b/outputs_xlsx_solution/test_new4.4-wide-NF-1.xlsx
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1926,10 +1932,26 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
         <v>35</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
